--- a/tame_output/ON/bt/strategyON_20231026.xlsx
+++ b/tame_output/ON/bt/strategyON_20231026.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>83.4%</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.7%</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.3%</t>
+          <t>-157.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.6%</t>
+          <t>131.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1761"/>
+  <dimension ref="A1:G1762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42013,7 +42013,7 @@
         <v>45223</v>
       </c>
       <c r="B1761" t="n">
-        <v>3.045961362411172</v>
+        <v>3.046980105223825</v>
       </c>
       <c r="C1761" t="n">
         <v>3.010249418375564</v>
@@ -42029,6 +42029,29 @@
       </c>
       <c r="G1761" t="n">
         <v>4.304695302344604</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="2" t="n">
+        <v>45224</v>
+      </c>
+      <c r="B1762" t="n">
+        <v>3.069622570279815</v>
+      </c>
+      <c r="C1762" t="n">
+        <v>3.010722978056604</v>
+      </c>
+      <c r="D1762" t="n">
+        <v>1.526918082248119</v>
+      </c>
+      <c r="E1762" t="n">
+        <v>3.621133786642105</v>
+      </c>
+      <c r="F1762" t="n">
+        <v>2.157409806615064</v>
+      </c>
+      <c r="G1762" t="n">
+        <v>4.305168862025645</v>
       </c>
     </row>
   </sheetData>
